--- a/Plan/Table/LiveData/07.GachaData.xlsx
+++ b/Plan/Table/LiveData/07.GachaData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B92A9D92-B191-4B58-916F-A87ECE299125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A6FC13F-FFCA-4E60-87AE-93DD617CBF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12915" yWindow="2835" windowWidth="14505" windowHeight="13485" xr2:uid="{1E5E59E1-4025-489D-877B-BD8401B40958}"/>
+    <workbookView xWindow="19500" yWindow="3720" windowWidth="14505" windowHeight="13485" xr2:uid="{AB6CC708-533C-42C2-B0F2-07485044D5BC}"/>
   </bookViews>
   <sheets>
     <sheet name="07.GachaData" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="62">
   <si>
     <t>No</t>
   </si>
@@ -159,6 +162,69 @@
   </si>
   <si>
     <t>Card_RiftStartumAnalysis_Enhanced</t>
+  </si>
+  <si>
+    <t>tra01</t>
+  </si>
+  <si>
+    <t>tra02</t>
+  </si>
+  <si>
+    <t>relic101</t>
+  </si>
+  <si>
+    <t>relic102</t>
+  </si>
+  <si>
+    <t>relic103</t>
+  </si>
+  <si>
+    <t>relic104</t>
+  </si>
+  <si>
+    <t>relic105</t>
+  </si>
+  <si>
+    <t>relic106</t>
+  </si>
+  <si>
+    <t>relic107</t>
+  </si>
+  <si>
+    <t>relic109</t>
+  </si>
+  <si>
+    <t>relic110</t>
+  </si>
+  <si>
+    <t>relic111</t>
+  </si>
+  <si>
+    <t>relic112</t>
+  </si>
+  <si>
+    <t>relic114</t>
+  </si>
+  <si>
+    <t>relic115</t>
+  </si>
+  <si>
+    <t>relic116</t>
+  </si>
+  <si>
+    <t>relic117</t>
+  </si>
+  <si>
+    <t>relic118</t>
+  </si>
+  <si>
+    <t>relic121</t>
+  </si>
+  <si>
+    <t>relic122</t>
+  </si>
+  <si>
+    <t>relic123</t>
   </si>
 </sst>
 </file>
@@ -541,9 +607,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88511EB4-E93B-48F3-8A72-82CFAA37F46D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40F966C-25A6-43EB-92AA-FB663A873E97}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -577,7 +643,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -600,7 +666,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -623,7 +689,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -646,7 +712,7 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -669,7 +735,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -692,7 +758,7 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -715,7 +781,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -738,7 +804,7 @@
         <v>1</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -761,7 +827,7 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -784,7 +850,7 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -807,7 +873,7 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -830,7 +896,7 @@
         <v>1</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -853,7 +919,7 @@
         <v>1</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -876,7 +942,7 @@
         <v>1</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -899,7 +965,7 @@
         <v>1</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -922,7 +988,7 @@
         <v>1</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -945,7 +1011,7 @@
         <v>1</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -968,7 +1034,7 @@
         <v>1</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -991,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1014,7 +1080,7 @@
         <v>1</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1037,7 +1103,7 @@
         <v>1</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1060,7 +1126,7 @@
         <v>1</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1083,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1106,7 +1172,7 @@
         <v>1</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1129,7 +1195,7 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1152,7 +1218,7 @@
         <v>1</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1175,7 +1241,7 @@
         <v>1</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -1198,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1221,7 +1287,7 @@
         <v>1</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1244,7 +1310,7 @@
         <v>1</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1267,7 +1333,7 @@
         <v>1</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1290,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1313,7 +1379,7 @@
         <v>1</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1336,7 +1402,7 @@
         <v>1</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1348,6 +1414,2145 @@
         <v>40</v>
       </c>
       <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36">
+        <v>101</v>
+      </c>
+      <c r="D36">
+        <v>1500</v>
+      </c>
+      <c r="E36">
+        <v>2</v>
+      </c>
+      <c r="F36" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>101</v>
+      </c>
+      <c r="D37">
+        <v>1500</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="F37" t="s">
+        <v>8</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>101</v>
+      </c>
+      <c r="D38">
+        <v>1500</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="F38" t="s">
+        <v>11</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
+        <v>101</v>
+      </c>
+      <c r="D39">
+        <v>1500</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="F39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
+        <v>101</v>
+      </c>
+      <c r="D40">
+        <v>429</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="F40" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41">
+        <v>101</v>
+      </c>
+      <c r="D41">
+        <v>429</v>
+      </c>
+      <c r="E41">
+        <v>2</v>
+      </c>
+      <c r="F41" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>101</v>
+      </c>
+      <c r="D42">
+        <v>429</v>
+      </c>
+      <c r="E42">
+        <v>2</v>
+      </c>
+      <c r="F42" t="s">
+        <v>19</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>101</v>
+      </c>
+      <c r="D43">
+        <v>429</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+      <c r="F43" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>101</v>
+      </c>
+      <c r="D44">
+        <v>428</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
+      </c>
+      <c r="F44" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>101</v>
+      </c>
+      <c r="D45">
+        <v>428</v>
+      </c>
+      <c r="E45">
+        <v>2</v>
+      </c>
+      <c r="F45" t="s">
+        <v>25</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>101</v>
+      </c>
+      <c r="D46">
+        <v>428</v>
+      </c>
+      <c r="E46">
+        <v>2</v>
+      </c>
+      <c r="F46" t="s">
+        <v>27</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>101</v>
+      </c>
+      <c r="D47">
+        <v>1000</v>
+      </c>
+      <c r="E47">
+        <v>2</v>
+      </c>
+      <c r="F47" t="s">
+        <v>39</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48">
+        <v>102</v>
+      </c>
+      <c r="D48">
+        <v>750</v>
+      </c>
+      <c r="E48">
+        <v>2</v>
+      </c>
+      <c r="F48" t="s">
+        <v>7</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49">
+        <v>102</v>
+      </c>
+      <c r="D49">
+        <v>750</v>
+      </c>
+      <c r="E49">
+        <v>2</v>
+      </c>
+      <c r="F49" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <v>102</v>
+      </c>
+      <c r="D50">
+        <v>750</v>
+      </c>
+      <c r="E50">
+        <v>2</v>
+      </c>
+      <c r="F50" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51">
+        <v>102</v>
+      </c>
+      <c r="D51">
+        <v>750</v>
+      </c>
+      <c r="E51">
+        <v>2</v>
+      </c>
+      <c r="F51" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52">
+        <v>102</v>
+      </c>
+      <c r="D52">
+        <v>215</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <v>102</v>
+      </c>
+      <c r="D53">
+        <v>215</v>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="F53" t="s">
+        <v>17</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <v>102</v>
+      </c>
+      <c r="D54">
+        <v>214</v>
+      </c>
+      <c r="E54">
+        <v>2</v>
+      </c>
+      <c r="F54" t="s">
+        <v>19</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55">
+        <v>102</v>
+      </c>
+      <c r="D55">
+        <v>214</v>
+      </c>
+      <c r="E55">
+        <v>2</v>
+      </c>
+      <c r="F55" t="s">
+        <v>21</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56">
+        <v>102</v>
+      </c>
+      <c r="D56">
+        <v>214</v>
+      </c>
+      <c r="E56">
+        <v>2</v>
+      </c>
+      <c r="F56" t="s">
+        <v>23</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57">
+        <v>102</v>
+      </c>
+      <c r="D57">
+        <v>214</v>
+      </c>
+      <c r="E57">
+        <v>2</v>
+      </c>
+      <c r="F57" t="s">
+        <v>25</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58">
+        <v>102</v>
+      </c>
+      <c r="D58">
+        <v>214</v>
+      </c>
+      <c r="E58">
+        <v>2</v>
+      </c>
+      <c r="F58" t="s">
+        <v>27</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59">
+        <v>102</v>
+      </c>
+      <c r="D59">
+        <v>500</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="F59" t="s">
+        <v>39</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60">
+        <v>102</v>
+      </c>
+      <c r="D60">
+        <v>750</v>
+      </c>
+      <c r="E60">
+        <v>2</v>
+      </c>
+      <c r="F60" t="s">
+        <v>9</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61">
+        <v>102</v>
+      </c>
+      <c r="D61">
+        <v>750</v>
+      </c>
+      <c r="E61">
+        <v>2</v>
+      </c>
+      <c r="F61" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62">
+        <v>102</v>
+      </c>
+      <c r="D62">
+        <v>750</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+      <c r="F62" t="s">
+        <v>12</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63">
+        <v>102</v>
+      </c>
+      <c r="D63">
+        <v>750</v>
+      </c>
+      <c r="E63">
+        <v>2</v>
+      </c>
+      <c r="F63" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+      <c r="C64">
+        <v>102</v>
+      </c>
+      <c r="D64">
+        <v>215</v>
+      </c>
+      <c r="E64">
+        <v>2</v>
+      </c>
+      <c r="F64" t="s">
+        <v>16</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65">
+        <v>102</v>
+      </c>
+      <c r="D65">
+        <v>215</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66">
+        <v>102</v>
+      </c>
+      <c r="D66">
+        <v>214</v>
+      </c>
+      <c r="E66">
+        <v>2</v>
+      </c>
+      <c r="F66" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67">
+        <v>102</v>
+      </c>
+      <c r="D67">
+        <v>214</v>
+      </c>
+      <c r="E67">
+        <v>2</v>
+      </c>
+      <c r="F67" t="s">
+        <v>22</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68">
+        <v>102</v>
+      </c>
+      <c r="D68">
+        <v>214</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="F68" t="s">
+        <v>24</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69">
+        <v>102</v>
+      </c>
+      <c r="D69">
+        <v>214</v>
+      </c>
+      <c r="E69">
+        <v>2</v>
+      </c>
+      <c r="F69" t="s">
+        <v>26</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70">
+        <v>102</v>
+      </c>
+      <c r="D70">
+        <v>214</v>
+      </c>
+      <c r="E70">
+        <v>2</v>
+      </c>
+      <c r="F70" t="s">
+        <v>28</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="C71">
+        <v>102</v>
+      </c>
+      <c r="D71">
+        <v>500</v>
+      </c>
+      <c r="E71">
+        <v>2</v>
+      </c>
+      <c r="F71" t="s">
+        <v>40</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
+      </c>
+      <c r="C72">
+        <v>1011</v>
+      </c>
+      <c r="D72">
+        <v>6500</v>
+      </c>
+      <c r="E72">
+        <v>4</v>
+      </c>
+      <c r="F72" t="s">
+        <v>41</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>2</v>
+      </c>
+      <c r="C73">
+        <v>1011</v>
+      </c>
+      <c r="D73">
+        <v>3500</v>
+      </c>
+      <c r="E73">
+        <v>4</v>
+      </c>
+      <c r="F73" t="s">
+        <v>42</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>2</v>
+      </c>
+      <c r="C74">
+        <v>1012</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74">
+        <v>3</v>
+      </c>
+      <c r="F74" t="s">
+        <v>43</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>2</v>
+      </c>
+      <c r="C75">
+        <v>1012</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75">
+        <v>3</v>
+      </c>
+      <c r="F75" t="s">
+        <v>44</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>2</v>
+      </c>
+      <c r="C76">
+        <v>1012</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>3</v>
+      </c>
+      <c r="F76" t="s">
+        <v>45</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>2</v>
+      </c>
+      <c r="C77">
+        <v>1012</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77">
+        <v>3</v>
+      </c>
+      <c r="F77" t="s">
+        <v>46</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+      <c r="C78">
+        <v>1012</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78">
+        <v>3</v>
+      </c>
+      <c r="F78" t="s">
+        <v>47</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+      <c r="C79">
+        <v>1012</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79">
+        <v>3</v>
+      </c>
+      <c r="F79" t="s">
+        <v>48</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>2</v>
+      </c>
+      <c r="C80">
+        <v>1012</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="E80">
+        <v>3</v>
+      </c>
+      <c r="F80" t="s">
+        <v>49</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>2</v>
+      </c>
+      <c r="C81">
+        <v>1012</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81">
+        <v>3</v>
+      </c>
+      <c r="F81" t="s">
+        <v>50</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>2</v>
+      </c>
+      <c r="C82">
+        <v>1012</v>
+      </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="E82">
+        <v>3</v>
+      </c>
+      <c r="F82" t="s">
+        <v>51</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>2</v>
+      </c>
+      <c r="C83">
+        <v>1012</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83">
+        <v>3</v>
+      </c>
+      <c r="F83" t="s">
+        <v>52</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>2</v>
+      </c>
+      <c r="C84">
+        <v>1012</v>
+      </c>
+      <c r="D84">
+        <v>1</v>
+      </c>
+      <c r="E84">
+        <v>3</v>
+      </c>
+      <c r="F84" t="s">
+        <v>53</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>2</v>
+      </c>
+      <c r="C85">
+        <v>1012</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="E85">
+        <v>3</v>
+      </c>
+      <c r="F85" t="s">
+        <v>54</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>2</v>
+      </c>
+      <c r="C86">
+        <v>1012</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86">
+        <v>3</v>
+      </c>
+      <c r="F86" t="s">
+        <v>55</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>2</v>
+      </c>
+      <c r="C87">
+        <v>1012</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="E87">
+        <v>3</v>
+      </c>
+      <c r="F87" t="s">
+        <v>56</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>2</v>
+      </c>
+      <c r="C88">
+        <v>1012</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="E88">
+        <v>3</v>
+      </c>
+      <c r="F88" t="s">
+        <v>57</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>2</v>
+      </c>
+      <c r="C89">
+        <v>1012</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>3</v>
+      </c>
+      <c r="F89" t="s">
+        <v>58</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>2</v>
+      </c>
+      <c r="C90">
+        <v>1012</v>
+      </c>
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="E90">
+        <v>3</v>
+      </c>
+      <c r="F90" t="s">
+        <v>59</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>2</v>
+      </c>
+      <c r="C91">
+        <v>1012</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91">
+        <v>3</v>
+      </c>
+      <c r="F91" t="s">
+        <v>60</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>2</v>
+      </c>
+      <c r="C92">
+        <v>1012</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92">
+        <v>3</v>
+      </c>
+      <c r="F92" t="s">
+        <v>61</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>2</v>
+      </c>
+      <c r="C93">
+        <v>1013</v>
+      </c>
+      <c r="D93">
+        <v>1200</v>
+      </c>
+      <c r="E93">
+        <v>2</v>
+      </c>
+      <c r="F93" t="s">
+        <v>7</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>2</v>
+      </c>
+      <c r="C94">
+        <v>1013</v>
+      </c>
+      <c r="D94">
+        <v>1200</v>
+      </c>
+      <c r="E94">
+        <v>2</v>
+      </c>
+      <c r="F94" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>2</v>
+      </c>
+      <c r="C95">
+        <v>1013</v>
+      </c>
+      <c r="D95">
+        <v>1200</v>
+      </c>
+      <c r="E95">
+        <v>2</v>
+      </c>
+      <c r="F95" t="s">
+        <v>11</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>2</v>
+      </c>
+      <c r="C96">
+        <v>1013</v>
+      </c>
+      <c r="D96">
+        <v>1200</v>
+      </c>
+      <c r="E96">
+        <v>2</v>
+      </c>
+      <c r="F96" t="s">
+        <v>13</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>2</v>
+      </c>
+      <c r="C97">
+        <v>1013</v>
+      </c>
+      <c r="D97">
+        <v>343</v>
+      </c>
+      <c r="E97">
+        <v>2</v>
+      </c>
+      <c r="F97" t="s">
+        <v>15</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>2</v>
+      </c>
+      <c r="C98">
+        <v>1013</v>
+      </c>
+      <c r="D98">
+        <v>343</v>
+      </c>
+      <c r="E98">
+        <v>2</v>
+      </c>
+      <c r="F98" t="s">
+        <v>17</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>2</v>
+      </c>
+      <c r="C99">
+        <v>1013</v>
+      </c>
+      <c r="D99">
+        <v>343</v>
+      </c>
+      <c r="E99">
+        <v>2</v>
+      </c>
+      <c r="F99" t="s">
+        <v>19</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>2</v>
+      </c>
+      <c r="C100">
+        <v>1013</v>
+      </c>
+      <c r="D100">
+        <v>343</v>
+      </c>
+      <c r="E100">
+        <v>2</v>
+      </c>
+      <c r="F100" t="s">
+        <v>21</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>2</v>
+      </c>
+      <c r="C101">
+        <v>1013</v>
+      </c>
+      <c r="D101">
+        <v>343</v>
+      </c>
+      <c r="E101">
+        <v>2</v>
+      </c>
+      <c r="F101" t="s">
+        <v>23</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>2</v>
+      </c>
+      <c r="C102">
+        <v>1013</v>
+      </c>
+      <c r="D102">
+        <v>343</v>
+      </c>
+      <c r="E102">
+        <v>2</v>
+      </c>
+      <c r="F102" t="s">
+        <v>25</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>2</v>
+      </c>
+      <c r="C103">
+        <v>1013</v>
+      </c>
+      <c r="D103">
+        <v>342</v>
+      </c>
+      <c r="E103">
+        <v>2</v>
+      </c>
+      <c r="F103" t="s">
+        <v>27</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>2</v>
+      </c>
+      <c r="C104">
+        <v>1013</v>
+      </c>
+      <c r="D104">
+        <v>800</v>
+      </c>
+      <c r="E104">
+        <v>2</v>
+      </c>
+      <c r="F104" t="s">
+        <v>39</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>2</v>
+      </c>
+      <c r="C105">
+        <v>1013</v>
+      </c>
+      <c r="D105">
+        <v>300</v>
+      </c>
+      <c r="E105">
+        <v>2</v>
+      </c>
+      <c r="F105" t="s">
+        <v>9</v>
+      </c>
+      <c r="G105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>2</v>
+      </c>
+      <c r="C106">
+        <v>1013</v>
+      </c>
+      <c r="D106">
+        <v>300</v>
+      </c>
+      <c r="E106">
+        <v>2</v>
+      </c>
+      <c r="F106" t="s">
+        <v>10</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>2</v>
+      </c>
+      <c r="C107">
+        <v>1013</v>
+      </c>
+      <c r="D107">
+        <v>300</v>
+      </c>
+      <c r="E107">
+        <v>2</v>
+      </c>
+      <c r="F107" t="s">
+        <v>12</v>
+      </c>
+      <c r="G107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>2</v>
+      </c>
+      <c r="C108">
+        <v>1013</v>
+      </c>
+      <c r="D108">
+        <v>300</v>
+      </c>
+      <c r="E108">
+        <v>2</v>
+      </c>
+      <c r="F108" t="s">
+        <v>14</v>
+      </c>
+      <c r="G108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>2</v>
+      </c>
+      <c r="C109">
+        <v>1013</v>
+      </c>
+      <c r="D109">
+        <v>86</v>
+      </c>
+      <c r="E109">
+        <v>2</v>
+      </c>
+      <c r="F109" t="s">
+        <v>16</v>
+      </c>
+      <c r="G109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>2</v>
+      </c>
+      <c r="C110">
+        <v>1013</v>
+      </c>
+      <c r="D110">
+        <v>86</v>
+      </c>
+      <c r="E110">
+        <v>2</v>
+      </c>
+      <c r="F110" t="s">
+        <v>18</v>
+      </c>
+      <c r="G110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>2</v>
+      </c>
+      <c r="C111">
+        <v>1013</v>
+      </c>
+      <c r="D111">
+        <v>86</v>
+      </c>
+      <c r="E111">
+        <v>2</v>
+      </c>
+      <c r="F111" t="s">
+        <v>20</v>
+      </c>
+      <c r="G111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>2</v>
+      </c>
+      <c r="C112">
+        <v>1013</v>
+      </c>
+      <c r="D112">
+        <v>86</v>
+      </c>
+      <c r="E112">
+        <v>2</v>
+      </c>
+      <c r="F112" t="s">
+        <v>22</v>
+      </c>
+      <c r="G112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>2</v>
+      </c>
+      <c r="C113">
+        <v>1013</v>
+      </c>
+      <c r="D113">
+        <v>86</v>
+      </c>
+      <c r="E113">
+        <v>2</v>
+      </c>
+      <c r="F113" t="s">
+        <v>24</v>
+      </c>
+      <c r="G113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>2</v>
+      </c>
+      <c r="C114">
+        <v>1013</v>
+      </c>
+      <c r="D114">
+        <v>85</v>
+      </c>
+      <c r="E114">
+        <v>2</v>
+      </c>
+      <c r="F114" t="s">
+        <v>26</v>
+      </c>
+      <c r="G114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>2</v>
+      </c>
+      <c r="C115">
+        <v>1013</v>
+      </c>
+      <c r="D115">
+        <v>85</v>
+      </c>
+      <c r="E115">
+        <v>2</v>
+      </c>
+      <c r="F115" t="s">
+        <v>28</v>
+      </c>
+      <c r="G115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>2</v>
+      </c>
+      <c r="C116">
+        <v>1013</v>
+      </c>
+      <c r="D116">
+        <v>200</v>
+      </c>
+      <c r="E116">
+        <v>2</v>
+      </c>
+      <c r="F116" t="s">
+        <v>40</v>
+      </c>
+      <c r="G116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>3</v>
+      </c>
+      <c r="C117">
+        <v>1101</v>
+      </c>
+      <c r="D117">
+        <v>1500</v>
+      </c>
+      <c r="E117">
+        <v>2</v>
+      </c>
+      <c r="F117" t="s">
+        <v>7</v>
+      </c>
+      <c r="G117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>3</v>
+      </c>
+      <c r="C118">
+        <v>1101</v>
+      </c>
+      <c r="D118">
+        <v>1500</v>
+      </c>
+      <c r="E118">
+        <v>2</v>
+      </c>
+      <c r="F118" t="s">
+        <v>8</v>
+      </c>
+      <c r="G118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>3</v>
+      </c>
+      <c r="C119">
+        <v>1101</v>
+      </c>
+      <c r="D119">
+        <v>1500</v>
+      </c>
+      <c r="E119">
+        <v>2</v>
+      </c>
+      <c r="F119" t="s">
+        <v>11</v>
+      </c>
+      <c r="G119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>3</v>
+      </c>
+      <c r="C120">
+        <v>1101</v>
+      </c>
+      <c r="D120">
+        <v>1500</v>
+      </c>
+      <c r="E120">
+        <v>2</v>
+      </c>
+      <c r="F120" t="s">
+        <v>13</v>
+      </c>
+      <c r="G120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>3</v>
+      </c>
+      <c r="C121">
+        <v>1101</v>
+      </c>
+      <c r="D121">
+        <v>429</v>
+      </c>
+      <c r="E121">
+        <v>2</v>
+      </c>
+      <c r="F121" t="s">
+        <v>15</v>
+      </c>
+      <c r="G121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>3</v>
+      </c>
+      <c r="C122">
+        <v>1101</v>
+      </c>
+      <c r="D122">
+        <v>429</v>
+      </c>
+      <c r="E122">
+        <v>2</v>
+      </c>
+      <c r="F122" t="s">
+        <v>17</v>
+      </c>
+      <c r="G122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>3</v>
+      </c>
+      <c r="C123">
+        <v>1101</v>
+      </c>
+      <c r="D123">
+        <v>429</v>
+      </c>
+      <c r="E123">
+        <v>2</v>
+      </c>
+      <c r="F123" t="s">
+        <v>19</v>
+      </c>
+      <c r="G123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>3</v>
+      </c>
+      <c r="C124">
+        <v>1101</v>
+      </c>
+      <c r="D124">
+        <v>429</v>
+      </c>
+      <c r="E124">
+        <v>2</v>
+      </c>
+      <c r="F124" t="s">
+        <v>21</v>
+      </c>
+      <c r="G124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>3</v>
+      </c>
+      <c r="C125">
+        <v>1101</v>
+      </c>
+      <c r="D125">
+        <v>428</v>
+      </c>
+      <c r="E125">
+        <v>2</v>
+      </c>
+      <c r="F125" t="s">
+        <v>23</v>
+      </c>
+      <c r="G125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>3</v>
+      </c>
+      <c r="C126">
+        <v>1101</v>
+      </c>
+      <c r="D126">
+        <v>428</v>
+      </c>
+      <c r="E126">
+        <v>2</v>
+      </c>
+      <c r="F126" t="s">
+        <v>25</v>
+      </c>
+      <c r="G126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>3</v>
+      </c>
+      <c r="C127">
+        <v>1101</v>
+      </c>
+      <c r="D127">
+        <v>428</v>
+      </c>
+      <c r="E127">
+        <v>2</v>
+      </c>
+      <c r="F127" t="s">
+        <v>27</v>
+      </c>
+      <c r="G127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>3</v>
+      </c>
+      <c r="C128">
+        <v>1101</v>
+      </c>
+      <c r="D128">
+        <v>1000</v>
+      </c>
+      <c r="E128">
+        <v>2</v>
+      </c>
+      <c r="F128" t="s">
+        <v>39</v>
+      </c>
+      <c r="G128">
         <v>1</v>
       </c>
     </row>

--- a/Plan/Table/LiveData/07.GachaData.xlsx
+++ b/Plan/Table/LiveData/07.GachaData.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A6FC13F-FFCA-4E60-87AE-93DD617CBF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{781772BD-0284-4A4B-988B-6288220AE1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19500" yWindow="3720" windowWidth="14505" windowHeight="13485" xr2:uid="{AB6CC708-533C-42C2-B0F2-07485044D5BC}"/>
+    <workbookView xWindow="19500" yWindow="3720" windowWidth="14505" windowHeight="13485" xr2:uid="{2B50E6D6-811F-4AF4-B84C-CAB9535799DF}"/>
   </bookViews>
   <sheets>
     <sheet name="07.GachaData" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
     <t>Reward_Type</t>
   </si>
   <si>
-    <t>Reward_Valuue</t>
+    <t>Reward_Value</t>
   </si>
   <si>
     <t>Reward_Count</t>
@@ -607,8 +607,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40F966C-25A6-43EB-92AA-FB663A873E97}">
-  <sheetPr codeName="Sheet1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23CC9066-DF10-4160-AF6F-DF7EC214310D}">
   <dimension ref="A1:G128"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/Plan/Table/LiveData/07.GachaData.xlsx
+++ b/Plan/Table/LiveData/07.GachaData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{781772BD-0284-4A4B-988B-6288220AE1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1178D91-B573-446D-9080-B424F21FD866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19500" yWindow="3720" windowWidth="14505" windowHeight="13485" xr2:uid="{2B50E6D6-811F-4AF4-B84C-CAB9535799DF}"/>
+    <workbookView xWindow="-28920" yWindow="5280" windowWidth="29040" windowHeight="15720" xr2:uid="{444F7976-4FE6-492B-80AD-452070F64E5F}"/>
   </bookViews>
   <sheets>
     <sheet name="07.GachaData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="62">
   <si>
     <t>No</t>
   </si>
@@ -607,8 +607,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23CC9066-DF10-4160-AF6F-DF7EC214310D}">
-  <dimension ref="A1:G128"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E8D2A74-1101-4E42-9152-4D28E4DD76B8}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:G171"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -3555,6 +3556,995 @@
         <v>1</v>
       </c>
     </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>4</v>
+      </c>
+      <c r="C129">
+        <v>10101</v>
+      </c>
+      <c r="D129">
+        <v>1000</v>
+      </c>
+      <c r="E129">
+        <v>2</v>
+      </c>
+      <c r="F129" t="s">
+        <v>15</v>
+      </c>
+      <c r="G129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>4</v>
+      </c>
+      <c r="C130">
+        <v>10101</v>
+      </c>
+      <c r="D130">
+        <v>1000</v>
+      </c>
+      <c r="E130">
+        <v>2</v>
+      </c>
+      <c r="F130" t="s">
+        <v>17</v>
+      </c>
+      <c r="G130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>4</v>
+      </c>
+      <c r="C131">
+        <v>10101</v>
+      </c>
+      <c r="D131">
+        <v>1000</v>
+      </c>
+      <c r="E131">
+        <v>2</v>
+      </c>
+      <c r="F131" t="s">
+        <v>19</v>
+      </c>
+      <c r="G131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>4</v>
+      </c>
+      <c r="C132">
+        <v>10101</v>
+      </c>
+      <c r="D132">
+        <v>1000</v>
+      </c>
+      <c r="E132">
+        <v>2</v>
+      </c>
+      <c r="F132" t="s">
+        <v>21</v>
+      </c>
+      <c r="G132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>4</v>
+      </c>
+      <c r="C133">
+        <v>10101</v>
+      </c>
+      <c r="D133">
+        <v>1000</v>
+      </c>
+      <c r="E133">
+        <v>2</v>
+      </c>
+      <c r="F133" t="s">
+        <v>23</v>
+      </c>
+      <c r="G133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>4</v>
+      </c>
+      <c r="C134">
+        <v>10101</v>
+      </c>
+      <c r="D134">
+        <v>1000</v>
+      </c>
+      <c r="E134">
+        <v>2</v>
+      </c>
+      <c r="F134" t="s">
+        <v>25</v>
+      </c>
+      <c r="G134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>4</v>
+      </c>
+      <c r="C135">
+        <v>10101</v>
+      </c>
+      <c r="D135">
+        <v>1000</v>
+      </c>
+      <c r="E135">
+        <v>2</v>
+      </c>
+      <c r="F135" t="s">
+        <v>27</v>
+      </c>
+      <c r="G135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>4</v>
+      </c>
+      <c r="C136">
+        <v>10101</v>
+      </c>
+      <c r="D136">
+        <v>3000</v>
+      </c>
+      <c r="E136">
+        <v>2</v>
+      </c>
+      <c r="F136" t="s">
+        <v>39</v>
+      </c>
+      <c r="G136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>4</v>
+      </c>
+      <c r="C137">
+        <v>10201</v>
+      </c>
+      <c r="D137">
+        <v>1000</v>
+      </c>
+      <c r="E137">
+        <v>2</v>
+      </c>
+      <c r="F137" t="s">
+        <v>16</v>
+      </c>
+      <c r="G137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>4</v>
+      </c>
+      <c r="C138">
+        <v>10201</v>
+      </c>
+      <c r="D138">
+        <v>1000</v>
+      </c>
+      <c r="E138">
+        <v>2</v>
+      </c>
+      <c r="F138" t="s">
+        <v>18</v>
+      </c>
+      <c r="G138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>4</v>
+      </c>
+      <c r="C139">
+        <v>10201</v>
+      </c>
+      <c r="D139">
+        <v>1000</v>
+      </c>
+      <c r="E139">
+        <v>2</v>
+      </c>
+      <c r="F139" t="s">
+        <v>20</v>
+      </c>
+      <c r="G139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>4</v>
+      </c>
+      <c r="C140">
+        <v>10201</v>
+      </c>
+      <c r="D140">
+        <v>1000</v>
+      </c>
+      <c r="E140">
+        <v>2</v>
+      </c>
+      <c r="F140" t="s">
+        <v>22</v>
+      </c>
+      <c r="G140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>4</v>
+      </c>
+      <c r="C141">
+        <v>10201</v>
+      </c>
+      <c r="D141">
+        <v>1000</v>
+      </c>
+      <c r="E141">
+        <v>2</v>
+      </c>
+      <c r="F141" t="s">
+        <v>24</v>
+      </c>
+      <c r="G141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>4</v>
+      </c>
+      <c r="C142">
+        <v>10201</v>
+      </c>
+      <c r="D142">
+        <v>1000</v>
+      </c>
+      <c r="E142">
+        <v>2</v>
+      </c>
+      <c r="F142" t="s">
+        <v>26</v>
+      </c>
+      <c r="G142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>4</v>
+      </c>
+      <c r="C143">
+        <v>10201</v>
+      </c>
+      <c r="D143">
+        <v>1000</v>
+      </c>
+      <c r="E143">
+        <v>2</v>
+      </c>
+      <c r="F143" t="s">
+        <v>28</v>
+      </c>
+      <c r="G143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>4</v>
+      </c>
+      <c r="C144">
+        <v>10201</v>
+      </c>
+      <c r="D144">
+        <v>3000</v>
+      </c>
+      <c r="E144">
+        <v>2</v>
+      </c>
+      <c r="F144" t="s">
+        <v>40</v>
+      </c>
+      <c r="G144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>4</v>
+      </c>
+      <c r="C145">
+        <v>10301</v>
+      </c>
+      <c r="D145">
+        <v>500</v>
+      </c>
+      <c r="E145">
+        <v>2</v>
+      </c>
+      <c r="F145" t="s">
+        <v>16</v>
+      </c>
+      <c r="G145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>4</v>
+      </c>
+      <c r="C146">
+        <v>10301</v>
+      </c>
+      <c r="D146">
+        <v>500</v>
+      </c>
+      <c r="E146">
+        <v>2</v>
+      </c>
+      <c r="F146" t="s">
+        <v>18</v>
+      </c>
+      <c r="G146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147">
+        <v>4</v>
+      </c>
+      <c r="C147">
+        <v>10301</v>
+      </c>
+      <c r="D147">
+        <v>500</v>
+      </c>
+      <c r="E147">
+        <v>2</v>
+      </c>
+      <c r="F147" t="s">
+        <v>20</v>
+      </c>
+      <c r="G147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>4</v>
+      </c>
+      <c r="C148">
+        <v>10301</v>
+      </c>
+      <c r="D148">
+        <v>500</v>
+      </c>
+      <c r="E148">
+        <v>2</v>
+      </c>
+      <c r="F148" t="s">
+        <v>22</v>
+      </c>
+      <c r="G148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>4</v>
+      </c>
+      <c r="C149">
+        <v>10301</v>
+      </c>
+      <c r="D149">
+        <v>500</v>
+      </c>
+      <c r="E149">
+        <v>2</v>
+      </c>
+      <c r="F149" t="s">
+        <v>24</v>
+      </c>
+      <c r="G149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>4</v>
+      </c>
+      <c r="C150">
+        <v>10301</v>
+      </c>
+      <c r="D150">
+        <v>500</v>
+      </c>
+      <c r="E150">
+        <v>2</v>
+      </c>
+      <c r="F150" t="s">
+        <v>26</v>
+      </c>
+      <c r="G150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>4</v>
+      </c>
+      <c r="C151">
+        <v>10301</v>
+      </c>
+      <c r="D151">
+        <v>500</v>
+      </c>
+      <c r="E151">
+        <v>2</v>
+      </c>
+      <c r="F151" t="s">
+        <v>28</v>
+      </c>
+      <c r="G151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>4</v>
+      </c>
+      <c r="C152">
+        <v>10301</v>
+      </c>
+      <c r="D152">
+        <v>6500</v>
+      </c>
+      <c r="E152">
+        <v>2</v>
+      </c>
+      <c r="F152" t="s">
+        <v>40</v>
+      </c>
+      <c r="G152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>4</v>
+      </c>
+      <c r="C153">
+        <v>10302</v>
+      </c>
+      <c r="D153">
+        <v>1</v>
+      </c>
+      <c r="E153">
+        <v>3</v>
+      </c>
+      <c r="F153" t="s">
+        <v>43</v>
+      </c>
+      <c r="G153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>4</v>
+      </c>
+      <c r="C154">
+        <v>10302</v>
+      </c>
+      <c r="D154">
+        <v>1</v>
+      </c>
+      <c r="E154">
+        <v>3</v>
+      </c>
+      <c r="F154" t="s">
+        <v>44</v>
+      </c>
+      <c r="G154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>4</v>
+      </c>
+      <c r="C155">
+        <v>10302</v>
+      </c>
+      <c r="D155">
+        <v>1</v>
+      </c>
+      <c r="E155">
+        <v>3</v>
+      </c>
+      <c r="F155" t="s">
+        <v>45</v>
+      </c>
+      <c r="G155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>4</v>
+      </c>
+      <c r="C156">
+        <v>10302</v>
+      </c>
+      <c r="D156">
+        <v>1</v>
+      </c>
+      <c r="E156">
+        <v>3</v>
+      </c>
+      <c r="F156" t="s">
+        <v>46</v>
+      </c>
+      <c r="G156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>4</v>
+      </c>
+      <c r="C157">
+        <v>10302</v>
+      </c>
+      <c r="D157">
+        <v>1</v>
+      </c>
+      <c r="E157">
+        <v>3</v>
+      </c>
+      <c r="F157" t="s">
+        <v>47</v>
+      </c>
+      <c r="G157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>4</v>
+      </c>
+      <c r="C158">
+        <v>10302</v>
+      </c>
+      <c r="D158">
+        <v>1</v>
+      </c>
+      <c r="E158">
+        <v>3</v>
+      </c>
+      <c r="F158" t="s">
+        <v>48</v>
+      </c>
+      <c r="G158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>4</v>
+      </c>
+      <c r="C159">
+        <v>10302</v>
+      </c>
+      <c r="D159">
+        <v>1</v>
+      </c>
+      <c r="E159">
+        <v>3</v>
+      </c>
+      <c r="F159" t="s">
+        <v>49</v>
+      </c>
+      <c r="G159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>4</v>
+      </c>
+      <c r="C160">
+        <v>10302</v>
+      </c>
+      <c r="D160">
+        <v>1</v>
+      </c>
+      <c r="E160">
+        <v>3</v>
+      </c>
+      <c r="F160" t="s">
+        <v>50</v>
+      </c>
+      <c r="G160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>4</v>
+      </c>
+      <c r="C161">
+        <v>10302</v>
+      </c>
+      <c r="D161">
+        <v>1</v>
+      </c>
+      <c r="E161">
+        <v>3</v>
+      </c>
+      <c r="F161" t="s">
+        <v>51</v>
+      </c>
+      <c r="G161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>4</v>
+      </c>
+      <c r="C162">
+        <v>10302</v>
+      </c>
+      <c r="D162">
+        <v>1</v>
+      </c>
+      <c r="E162">
+        <v>3</v>
+      </c>
+      <c r="F162" t="s">
+        <v>52</v>
+      </c>
+      <c r="G162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>4</v>
+      </c>
+      <c r="C163">
+        <v>10302</v>
+      </c>
+      <c r="D163">
+        <v>1</v>
+      </c>
+      <c r="E163">
+        <v>3</v>
+      </c>
+      <c r="F163" t="s">
+        <v>53</v>
+      </c>
+      <c r="G163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>4</v>
+      </c>
+      <c r="C164">
+        <v>10302</v>
+      </c>
+      <c r="D164">
+        <v>1</v>
+      </c>
+      <c r="E164">
+        <v>3</v>
+      </c>
+      <c r="F164" t="s">
+        <v>54</v>
+      </c>
+      <c r="G164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>4</v>
+      </c>
+      <c r="C165">
+        <v>10302</v>
+      </c>
+      <c r="D165">
+        <v>1</v>
+      </c>
+      <c r="E165">
+        <v>3</v>
+      </c>
+      <c r="F165" t="s">
+        <v>55</v>
+      </c>
+      <c r="G165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>4</v>
+      </c>
+      <c r="C166">
+        <v>10302</v>
+      </c>
+      <c r="D166">
+        <v>1</v>
+      </c>
+      <c r="E166">
+        <v>3</v>
+      </c>
+      <c r="F166" t="s">
+        <v>56</v>
+      </c>
+      <c r="G166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>4</v>
+      </c>
+      <c r="C167">
+        <v>10302</v>
+      </c>
+      <c r="D167">
+        <v>1</v>
+      </c>
+      <c r="E167">
+        <v>3</v>
+      </c>
+      <c r="F167" t="s">
+        <v>57</v>
+      </c>
+      <c r="G167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>4</v>
+      </c>
+      <c r="C168">
+        <v>10302</v>
+      </c>
+      <c r="D168">
+        <v>1</v>
+      </c>
+      <c r="E168">
+        <v>3</v>
+      </c>
+      <c r="F168" t="s">
+        <v>58</v>
+      </c>
+      <c r="G168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>4</v>
+      </c>
+      <c r="C169">
+        <v>10302</v>
+      </c>
+      <c r="D169">
+        <v>1</v>
+      </c>
+      <c r="E169">
+        <v>3</v>
+      </c>
+      <c r="F169" t="s">
+        <v>59</v>
+      </c>
+      <c r="G169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>4</v>
+      </c>
+      <c r="C170">
+        <v>10302</v>
+      </c>
+      <c r="D170">
+        <v>1</v>
+      </c>
+      <c r="E170">
+        <v>3</v>
+      </c>
+      <c r="F170" t="s">
+        <v>60</v>
+      </c>
+      <c r="G170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>4</v>
+      </c>
+      <c r="C171">
+        <v>10302</v>
+      </c>
+      <c r="D171">
+        <v>1</v>
+      </c>
+      <c r="E171">
+        <v>3</v>
+      </c>
+      <c r="F171" t="s">
+        <v>61</v>
+      </c>
+      <c r="G171">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Plan/Table/LiveData/07.GachaData.xlsx
+++ b/Plan/Table/LiveData/07.GachaData.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1178D91-B573-446D-9080-B424F21FD866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{302155DF-24B9-4687-8FA9-4173BF118A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5280" windowWidth="29040" windowHeight="15720" xr2:uid="{444F7976-4FE6-492B-80AD-452070F64E5F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{0550C468-C19F-473C-B81B-1457D894D28B}"/>
   </bookViews>
   <sheets>
     <sheet name="07.GachaData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="60">
   <si>
     <t>No</t>
   </si>
@@ -164,6 +164,30 @@
     <t>Card_RiftStartumAnalysis_Enhanced</t>
   </si>
   <si>
+    <t>Card_Dummy_200</t>
+  </si>
+  <si>
+    <t>Card_Dummy_100</t>
+  </si>
+  <si>
+    <t>Card_Dummy_300</t>
+  </si>
+  <si>
+    <t>Card_Dummy_400</t>
+  </si>
+  <si>
+    <t>Card_Dummy_201</t>
+  </si>
+  <si>
+    <t>Card_Dummy_101</t>
+  </si>
+  <si>
+    <t>Card_Dummy_301</t>
+  </si>
+  <si>
+    <t>Card_Dummy_401</t>
+  </si>
+  <si>
     <t>tra01</t>
   </si>
   <si>
@@ -176,30 +200,12 @@
     <t>relic102</t>
   </si>
   <si>
-    <t>relic103</t>
-  </si>
-  <si>
-    <t>relic104</t>
-  </si>
-  <si>
-    <t>relic105</t>
-  </si>
-  <si>
-    <t>relic106</t>
-  </si>
-  <si>
     <t>relic107</t>
   </si>
   <si>
     <t>relic109</t>
   </si>
   <si>
-    <t>relic110</t>
-  </si>
-  <si>
-    <t>relic111</t>
-  </si>
-  <si>
     <t>relic112</t>
   </si>
   <si>
@@ -213,18 +219,6 @@
   </si>
   <si>
     <t>relic117</t>
-  </si>
-  <si>
-    <t>relic118</t>
-  </si>
-  <si>
-    <t>relic121</t>
-  </si>
-  <si>
-    <t>relic122</t>
-  </si>
-  <si>
-    <t>relic123</t>
   </si>
 </sst>
 </file>
@@ -607,9 +601,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E8D2A74-1101-4E42-9152-4D28E4DD76B8}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:G171"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DF6B4AC-4F08-4765-92F5-71256FAA6A8C}">
+  <dimension ref="A1:G178"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1520,7 +1513,7 @@
         <v>101</v>
       </c>
       <c r="D40">
-        <v>429</v>
+        <v>375</v>
       </c>
       <c r="E40">
         <v>2</v>
@@ -1543,7 +1536,7 @@
         <v>101</v>
       </c>
       <c r="D41">
-        <v>429</v>
+        <v>375</v>
       </c>
       <c r="E41">
         <v>2</v>
@@ -1566,7 +1559,7 @@
         <v>101</v>
       </c>
       <c r="D42">
-        <v>429</v>
+        <v>375</v>
       </c>
       <c r="E42">
         <v>2</v>
@@ -1589,7 +1582,7 @@
         <v>101</v>
       </c>
       <c r="D43">
-        <v>429</v>
+        <v>375</v>
       </c>
       <c r="E43">
         <v>2</v>
@@ -1612,7 +1605,7 @@
         <v>101</v>
       </c>
       <c r="D44">
-        <v>428</v>
+        <v>375</v>
       </c>
       <c r="E44">
         <v>2</v>
@@ -1635,7 +1628,7 @@
         <v>101</v>
       </c>
       <c r="D45">
-        <v>428</v>
+        <v>375</v>
       </c>
       <c r="E45">
         <v>2</v>
@@ -1658,7 +1651,7 @@
         <v>101</v>
       </c>
       <c r="D46">
-        <v>428</v>
+        <v>375</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -1681,13 +1674,13 @@
         <v>101</v>
       </c>
       <c r="D47">
-        <v>1000</v>
+        <v>375</v>
       </c>
       <c r="E47">
         <v>2</v>
       </c>
       <c r="F47" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -1701,16 +1694,16 @@
         <v>1</v>
       </c>
       <c r="C48">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D48">
-        <v>750</v>
+        <v>333</v>
       </c>
       <c r="E48">
         <v>2</v>
       </c>
       <c r="F48" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -1724,16 +1717,16 @@
         <v>1</v>
       </c>
       <c r="C49">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D49">
-        <v>750</v>
+        <v>333</v>
       </c>
       <c r="E49">
         <v>2</v>
       </c>
       <c r="F49" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -1747,16 +1740,16 @@
         <v>1</v>
       </c>
       <c r="C50">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D50">
-        <v>750</v>
+        <v>333</v>
       </c>
       <c r="E50">
         <v>2</v>
       </c>
       <c r="F50" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -1779,7 +1772,7 @@
         <v>2</v>
       </c>
       <c r="F51" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -1796,13 +1789,13 @@
         <v>102</v>
       </c>
       <c r="D52">
-        <v>215</v>
+        <v>750</v>
       </c>
       <c r="E52">
         <v>2</v>
       </c>
       <c r="F52" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -1819,13 +1812,13 @@
         <v>102</v>
       </c>
       <c r="D53">
-        <v>215</v>
+        <v>750</v>
       </c>
       <c r="E53">
         <v>2</v>
       </c>
       <c r="F53" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -1842,13 +1835,13 @@
         <v>102</v>
       </c>
       <c r="D54">
-        <v>214</v>
+        <v>750</v>
       </c>
       <c r="E54">
         <v>2</v>
       </c>
       <c r="F54" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -1865,13 +1858,13 @@
         <v>102</v>
       </c>
       <c r="D55">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="E55">
         <v>2</v>
       </c>
       <c r="F55" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -1888,13 +1881,13 @@
         <v>102</v>
       </c>
       <c r="D56">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="E56">
         <v>2</v>
       </c>
       <c r="F56" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -1911,13 +1904,13 @@
         <v>102</v>
       </c>
       <c r="D57">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="E57">
         <v>2</v>
       </c>
       <c r="F57" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -1934,13 +1927,13 @@
         <v>102</v>
       </c>
       <c r="D58">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="E58">
         <v>2</v>
       </c>
       <c r="F58" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -1957,13 +1950,13 @@
         <v>102</v>
       </c>
       <c r="D59">
-        <v>500</v>
+        <v>187</v>
       </c>
       <c r="E59">
         <v>2</v>
       </c>
       <c r="F59" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -1980,13 +1973,13 @@
         <v>102</v>
       </c>
       <c r="D60">
-        <v>750</v>
+        <v>187</v>
       </c>
       <c r="E60">
         <v>2</v>
       </c>
       <c r="F60" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -2003,13 +1996,13 @@
         <v>102</v>
       </c>
       <c r="D61">
-        <v>750</v>
+        <v>187</v>
       </c>
       <c r="E61">
         <v>2</v>
       </c>
       <c r="F61" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -2026,13 +2019,13 @@
         <v>102</v>
       </c>
       <c r="D62">
-        <v>750</v>
+        <v>187</v>
       </c>
       <c r="E62">
         <v>2</v>
       </c>
       <c r="F62" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -2049,13 +2042,13 @@
         <v>102</v>
       </c>
       <c r="D63">
-        <v>750</v>
+        <v>166</v>
       </c>
       <c r="E63">
         <v>2</v>
       </c>
       <c r="F63" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -2072,13 +2065,13 @@
         <v>102</v>
       </c>
       <c r="D64">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="E64">
         <v>2</v>
       </c>
       <c r="F64" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -2095,13 +2088,13 @@
         <v>102</v>
       </c>
       <c r="D65">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="E65">
         <v>2</v>
       </c>
       <c r="F65" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -2118,13 +2111,13 @@
         <v>102</v>
       </c>
       <c r="D66">
-        <v>214</v>
+        <v>750</v>
       </c>
       <c r="E66">
         <v>2</v>
       </c>
       <c r="F66" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -2141,13 +2134,13 @@
         <v>102</v>
       </c>
       <c r="D67">
-        <v>214</v>
+        <v>750</v>
       </c>
       <c r="E67">
         <v>2</v>
       </c>
       <c r="F67" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -2164,13 +2157,13 @@
         <v>102</v>
       </c>
       <c r="D68">
-        <v>214</v>
+        <v>750</v>
       </c>
       <c r="E68">
         <v>2</v>
       </c>
       <c r="F68" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -2187,13 +2180,13 @@
         <v>102</v>
       </c>
       <c r="D69">
-        <v>214</v>
+        <v>750</v>
       </c>
       <c r="E69">
         <v>2</v>
       </c>
       <c r="F69" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -2210,13 +2203,13 @@
         <v>102</v>
       </c>
       <c r="D70">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="E70">
         <v>2</v>
       </c>
       <c r="F70" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -2233,13 +2226,13 @@
         <v>102</v>
       </c>
       <c r="D71">
-        <v>500</v>
+        <v>187</v>
       </c>
       <c r="E71">
         <v>2</v>
       </c>
       <c r="F71" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -2250,19 +2243,19 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>1011</v>
+        <v>102</v>
       </c>
       <c r="D72">
-        <v>6500</v>
+        <v>187</v>
       </c>
       <c r="E72">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F72" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -2273,19 +2266,19 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>1011</v>
+        <v>102</v>
       </c>
       <c r="D73">
-        <v>3500</v>
+        <v>187</v>
       </c>
       <c r="E73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F73" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -2296,19 +2289,19 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>1012</v>
+        <v>102</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>187</v>
       </c>
       <c r="E74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F74" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -2319,19 +2312,19 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>1012</v>
+        <v>102</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>187</v>
       </c>
       <c r="E75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F75" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -2342,19 +2335,19 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>1012</v>
+        <v>102</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>187</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F76" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -2365,19 +2358,19 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>1012</v>
+        <v>102</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>187</v>
       </c>
       <c r="E77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F77" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -2388,19 +2381,19 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>1012</v>
+        <v>102</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>166</v>
       </c>
       <c r="E78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F78" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -2411,19 +2404,19 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>1012</v>
+        <v>102</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>167</v>
       </c>
       <c r="E79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F79" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -2434,19 +2427,19 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>1012</v>
+        <v>102</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>167</v>
       </c>
       <c r="E80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F80" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -2460,16 +2453,16 @@
         <v>2</v>
       </c>
       <c r="C81">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>6500</v>
       </c>
       <c r="E81">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F81" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -2483,16 +2476,16 @@
         <v>2</v>
       </c>
       <c r="C82">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>3500</v>
       </c>
       <c r="E82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -2515,7 +2508,7 @@
         <v>3</v>
       </c>
       <c r="F83" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -2538,7 +2531,7 @@
         <v>3</v>
       </c>
       <c r="F84" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -2561,7 +2554,7 @@
         <v>3</v>
       </c>
       <c r="F85" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -2584,7 +2577,7 @@
         <v>3</v>
       </c>
       <c r="F86" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -2607,7 +2600,7 @@
         <v>3</v>
       </c>
       <c r="F87" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -2630,7 +2623,7 @@
         <v>3</v>
       </c>
       <c r="F88" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -2653,7 +2646,7 @@
         <v>3</v>
       </c>
       <c r="F89" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -2676,7 +2669,7 @@
         <v>3</v>
       </c>
       <c r="F90" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -2699,7 +2692,7 @@
         <v>3</v>
       </c>
       <c r="F91" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -2713,16 +2706,16 @@
         <v>2</v>
       </c>
       <c r="C92">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="E92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F92" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -2745,7 +2738,7 @@
         <v>2</v>
       </c>
       <c r="F93" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -2768,7 +2761,7 @@
         <v>2</v>
       </c>
       <c r="F94" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G94">
         <v>1</v>
@@ -2791,7 +2784,7 @@
         <v>2</v>
       </c>
       <c r="F95" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -2808,13 +2801,13 @@
         <v>1013</v>
       </c>
       <c r="D96">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="E96">
         <v>2</v>
       </c>
       <c r="F96" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -2831,13 +2824,13 @@
         <v>1013</v>
       </c>
       <c r="D97">
-        <v>343</v>
+        <v>300</v>
       </c>
       <c r="E97">
         <v>2</v>
       </c>
       <c r="F97" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -2854,13 +2847,13 @@
         <v>1013</v>
       </c>
       <c r="D98">
-        <v>343</v>
+        <v>300</v>
       </c>
       <c r="E98">
         <v>2</v>
       </c>
       <c r="F98" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G98">
         <v>1</v>
@@ -2877,13 +2870,13 @@
         <v>1013</v>
       </c>
       <c r="D99">
-        <v>343</v>
+        <v>300</v>
       </c>
       <c r="E99">
         <v>2</v>
       </c>
       <c r="F99" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G99">
         <v>1</v>
@@ -2900,13 +2893,13 @@
         <v>1013</v>
       </c>
       <c r="D100">
-        <v>343</v>
+        <v>300</v>
       </c>
       <c r="E100">
         <v>2</v>
       </c>
       <c r="F100" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -2923,13 +2916,13 @@
         <v>1013</v>
       </c>
       <c r="D101">
-        <v>343</v>
+        <v>300</v>
       </c>
       <c r="E101">
         <v>2</v>
       </c>
       <c r="F101" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G101">
         <v>1</v>
@@ -2946,13 +2939,13 @@
         <v>1013</v>
       </c>
       <c r="D102">
-        <v>343</v>
+        <v>300</v>
       </c>
       <c r="E102">
         <v>2</v>
       </c>
       <c r="F102" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G102">
         <v>1</v>
@@ -2969,13 +2962,13 @@
         <v>1013</v>
       </c>
       <c r="D103">
-        <v>342</v>
+        <v>267</v>
       </c>
       <c r="E103">
         <v>2</v>
       </c>
       <c r="F103" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G103">
         <v>1</v>
@@ -2992,13 +2985,13 @@
         <v>1013</v>
       </c>
       <c r="D104">
-        <v>800</v>
+        <v>267</v>
       </c>
       <c r="E104">
         <v>2</v>
       </c>
       <c r="F104" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G104">
         <v>1</v>
@@ -3015,13 +3008,13 @@
         <v>1013</v>
       </c>
       <c r="D105">
-        <v>300</v>
+        <v>266</v>
       </c>
       <c r="E105">
         <v>2</v>
       </c>
       <c r="F105" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="G105">
         <v>1</v>
@@ -3038,13 +3031,13 @@
         <v>1013</v>
       </c>
       <c r="D106">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E106">
         <v>2</v>
       </c>
       <c r="F106" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="G106">
         <v>1</v>
@@ -3067,7 +3060,7 @@
         <v>2</v>
       </c>
       <c r="F107" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G107">
         <v>1</v>
@@ -3090,7 +3083,7 @@
         <v>2</v>
       </c>
       <c r="F108" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G108">
         <v>1</v>
@@ -3107,13 +3100,13 @@
         <v>1013</v>
       </c>
       <c r="D109">
-        <v>86</v>
+        <v>300</v>
       </c>
       <c r="E109">
         <v>2</v>
       </c>
       <c r="F109" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G109">
         <v>1</v>
@@ -3130,13 +3123,13 @@
         <v>1013</v>
       </c>
       <c r="D110">
-        <v>86</v>
+        <v>300</v>
       </c>
       <c r="E110">
         <v>2</v>
       </c>
       <c r="F110" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G110">
         <v>1</v>
@@ -3153,13 +3146,13 @@
         <v>1013</v>
       </c>
       <c r="D111">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E111">
         <v>2</v>
       </c>
       <c r="F111" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G111">
         <v>1</v>
@@ -3176,13 +3169,13 @@
         <v>1013</v>
       </c>
       <c r="D112">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E112">
         <v>2</v>
       </c>
       <c r="F112" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G112">
         <v>1</v>
@@ -3199,13 +3192,13 @@
         <v>1013</v>
       </c>
       <c r="D113">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E113">
         <v>2</v>
       </c>
       <c r="F113" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G113">
         <v>1</v>
@@ -3222,13 +3215,13 @@
         <v>1013</v>
       </c>
       <c r="D114">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E114">
         <v>2</v>
       </c>
       <c r="F114" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G114">
         <v>1</v>
@@ -3245,13 +3238,13 @@
         <v>1013</v>
       </c>
       <c r="D115">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E115">
         <v>2</v>
       </c>
       <c r="F115" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G115">
         <v>1</v>
@@ -3268,13 +3261,13 @@
         <v>1013</v>
       </c>
       <c r="D116">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="E116">
         <v>2</v>
       </c>
       <c r="F116" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="G116">
         <v>1</v>
@@ -3285,19 +3278,19 @@
         <v>116</v>
       </c>
       <c r="B117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>1101</v>
+        <v>1013</v>
       </c>
       <c r="D117">
-        <v>1500</v>
+        <v>75</v>
       </c>
       <c r="E117">
         <v>2</v>
       </c>
       <c r="F117" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="G117">
         <v>1</v>
@@ -3308,19 +3301,19 @@
         <v>117</v>
       </c>
       <c r="B118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C118">
-        <v>1101</v>
+        <v>1013</v>
       </c>
       <c r="D118">
-        <v>1500</v>
+        <v>75</v>
       </c>
       <c r="E118">
         <v>2</v>
       </c>
       <c r="F118" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -3331,19 +3324,19 @@
         <v>118</v>
       </c>
       <c r="B119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C119">
-        <v>1101</v>
+        <v>1013</v>
       </c>
       <c r="D119">
-        <v>1500</v>
+        <v>66</v>
       </c>
       <c r="E119">
         <v>2</v>
       </c>
       <c r="F119" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="G119">
         <v>1</v>
@@ -3354,19 +3347,19 @@
         <v>119</v>
       </c>
       <c r="B120">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C120">
-        <v>1101</v>
+        <v>1013</v>
       </c>
       <c r="D120">
-        <v>1500</v>
+        <v>67</v>
       </c>
       <c r="E120">
         <v>2</v>
       </c>
       <c r="F120" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="G120">
         <v>1</v>
@@ -3377,19 +3370,19 @@
         <v>120</v>
       </c>
       <c r="B121">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>1101</v>
+        <v>1013</v>
       </c>
       <c r="D121">
-        <v>429</v>
+        <v>67</v>
       </c>
       <c r="E121">
         <v>2</v>
       </c>
       <c r="F121" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="G121">
         <v>1</v>
@@ -3406,13 +3399,13 @@
         <v>1101</v>
       </c>
       <c r="D122">
-        <v>429</v>
+        <v>1500</v>
       </c>
       <c r="E122">
         <v>2</v>
       </c>
       <c r="F122" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G122">
         <v>1</v>
@@ -3429,13 +3422,13 @@
         <v>1101</v>
       </c>
       <c r="D123">
-        <v>429</v>
+        <v>1500</v>
       </c>
       <c r="E123">
         <v>2</v>
       </c>
       <c r="F123" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G123">
         <v>1</v>
@@ -3452,13 +3445,13 @@
         <v>1101</v>
       </c>
       <c r="D124">
-        <v>429</v>
+        <v>1500</v>
       </c>
       <c r="E124">
         <v>2</v>
       </c>
       <c r="F124" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G124">
         <v>1</v>
@@ -3475,13 +3468,13 @@
         <v>1101</v>
       </c>
       <c r="D125">
-        <v>428</v>
+        <v>1500</v>
       </c>
       <c r="E125">
         <v>2</v>
       </c>
       <c r="F125" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G125">
         <v>1</v>
@@ -3498,13 +3491,13 @@
         <v>1101</v>
       </c>
       <c r="D126">
-        <v>428</v>
+        <v>375</v>
       </c>
       <c r="E126">
         <v>2</v>
       </c>
       <c r="F126" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G126">
         <v>1</v>
@@ -3521,13 +3514,13 @@
         <v>1101</v>
       </c>
       <c r="D127">
-        <v>428</v>
+        <v>375</v>
       </c>
       <c r="E127">
         <v>2</v>
       </c>
       <c r="F127" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G127">
         <v>1</v>
@@ -3544,13 +3537,13 @@
         <v>1101</v>
       </c>
       <c r="D128">
-        <v>1000</v>
+        <v>375</v>
       </c>
       <c r="E128">
         <v>2</v>
       </c>
       <c r="F128" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -3561,19 +3554,19 @@
         <v>128</v>
       </c>
       <c r="B129">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C129">
-        <v>10101</v>
+        <v>1101</v>
       </c>
       <c r="D129">
-        <v>1000</v>
+        <v>375</v>
       </c>
       <c r="E129">
         <v>2</v>
       </c>
       <c r="F129" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G129">
         <v>1</v>
@@ -3584,19 +3577,19 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C130">
-        <v>10101</v>
+        <v>1101</v>
       </c>
       <c r="D130">
-        <v>1000</v>
+        <v>375</v>
       </c>
       <c r="E130">
         <v>2</v>
       </c>
       <c r="F130" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -3607,19 +3600,19 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>10101</v>
+        <v>1101</v>
       </c>
       <c r="D131">
-        <v>1000</v>
+        <v>375</v>
       </c>
       <c r="E131">
         <v>2</v>
       </c>
       <c r="F131" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -3630,19 +3623,19 @@
         <v>131</v>
       </c>
       <c r="B132">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C132">
-        <v>10101</v>
+        <v>1101</v>
       </c>
       <c r="D132">
-        <v>1000</v>
+        <v>375</v>
       </c>
       <c r="E132">
         <v>2</v>
       </c>
       <c r="F132" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -3653,19 +3646,19 @@
         <v>132</v>
       </c>
       <c r="B133">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C133">
-        <v>10101</v>
+        <v>1101</v>
       </c>
       <c r="D133">
-        <v>1000</v>
+        <v>375</v>
       </c>
       <c r="E133">
         <v>2</v>
       </c>
       <c r="F133" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -3676,19 +3669,19 @@
         <v>133</v>
       </c>
       <c r="B134">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C134">
-        <v>10101</v>
+        <v>1101</v>
       </c>
       <c r="D134">
-        <v>1000</v>
+        <v>333</v>
       </c>
       <c r="E134">
         <v>2</v>
       </c>
       <c r="F134" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G134">
         <v>1</v>
@@ -3699,19 +3692,19 @@
         <v>134</v>
       </c>
       <c r="B135">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C135">
-        <v>10101</v>
+        <v>1101</v>
       </c>
       <c r="D135">
-        <v>1000</v>
+        <v>334</v>
       </c>
       <c r="E135">
         <v>2</v>
       </c>
       <c r="F135" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="G135">
         <v>1</v>
@@ -3722,19 +3715,19 @@
         <v>135</v>
       </c>
       <c r="B136">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C136">
-        <v>10101</v>
+        <v>1101</v>
       </c>
       <c r="D136">
-        <v>3000</v>
+        <v>333</v>
       </c>
       <c r="E136">
         <v>2</v>
       </c>
       <c r="F136" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G136">
         <v>1</v>
@@ -3748,16 +3741,16 @@
         <v>4</v>
       </c>
       <c r="C137">
-        <v>10201</v>
+        <v>10101</v>
       </c>
       <c r="D137">
-        <v>1000</v>
+        <v>875</v>
       </c>
       <c r="E137">
         <v>2</v>
       </c>
       <c r="F137" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G137">
         <v>1</v>
@@ -3771,16 +3764,16 @@
         <v>4</v>
       </c>
       <c r="C138">
-        <v>10201</v>
+        <v>10101</v>
       </c>
       <c r="D138">
-        <v>1000</v>
+        <v>875</v>
       </c>
       <c r="E138">
         <v>2</v>
       </c>
       <c r="F138" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G138">
         <v>1</v>
@@ -3794,16 +3787,16 @@
         <v>4</v>
       </c>
       <c r="C139">
-        <v>10201</v>
+        <v>10101</v>
       </c>
       <c r="D139">
-        <v>1000</v>
+        <v>875</v>
       </c>
       <c r="E139">
         <v>2</v>
       </c>
       <c r="F139" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G139">
         <v>1</v>
@@ -3817,16 +3810,16 @@
         <v>4</v>
       </c>
       <c r="C140">
-        <v>10201</v>
+        <v>10101</v>
       </c>
       <c r="D140">
-        <v>1000</v>
+        <v>875</v>
       </c>
       <c r="E140">
         <v>2</v>
       </c>
       <c r="F140" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G140">
         <v>1</v>
@@ -3840,16 +3833,16 @@
         <v>4</v>
       </c>
       <c r="C141">
-        <v>10201</v>
+        <v>10101</v>
       </c>
       <c r="D141">
-        <v>1000</v>
+        <v>875</v>
       </c>
       <c r="E141">
         <v>2</v>
       </c>
       <c r="F141" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -3863,16 +3856,16 @@
         <v>4</v>
       </c>
       <c r="C142">
-        <v>10201</v>
+        <v>10101</v>
       </c>
       <c r="D142">
-        <v>1000</v>
+        <v>875</v>
       </c>
       <c r="E142">
         <v>2</v>
       </c>
       <c r="F142" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -3886,16 +3879,16 @@
         <v>4</v>
       </c>
       <c r="C143">
-        <v>10201</v>
+        <v>10101</v>
       </c>
       <c r="D143">
-        <v>1000</v>
+        <v>875</v>
       </c>
       <c r="E143">
         <v>2</v>
       </c>
       <c r="F143" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G143">
         <v>1</v>
@@ -3909,16 +3902,16 @@
         <v>4</v>
       </c>
       <c r="C144">
-        <v>10201</v>
+        <v>10101</v>
       </c>
       <c r="D144">
-        <v>3000</v>
+        <v>875</v>
       </c>
       <c r="E144">
         <v>2</v>
       </c>
       <c r="F144" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G144">
         <v>1</v>
@@ -3932,16 +3925,16 @@
         <v>4</v>
       </c>
       <c r="C145">
-        <v>10301</v>
+        <v>10101</v>
       </c>
       <c r="D145">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="E145">
         <v>2</v>
       </c>
       <c r="F145" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G145">
         <v>1</v>
@@ -3955,16 +3948,16 @@
         <v>4</v>
       </c>
       <c r="C146">
-        <v>10301</v>
+        <v>10101</v>
       </c>
       <c r="D146">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="E146">
         <v>2</v>
       </c>
       <c r="F146" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="G146">
         <v>1</v>
@@ -3978,16 +3971,16 @@
         <v>4</v>
       </c>
       <c r="C147">
-        <v>10301</v>
+        <v>10101</v>
       </c>
       <c r="D147">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="E147">
         <v>2</v>
       </c>
       <c r="F147" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G147">
         <v>1</v>
@@ -4001,16 +3994,16 @@
         <v>4</v>
       </c>
       <c r="C148">
-        <v>10301</v>
+        <v>10201</v>
       </c>
       <c r="D148">
-        <v>500</v>
+        <v>875</v>
       </c>
       <c r="E148">
         <v>2</v>
       </c>
       <c r="F148" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G148">
         <v>1</v>
@@ -4024,16 +4017,16 @@
         <v>4</v>
       </c>
       <c r="C149">
-        <v>10301</v>
+        <v>10201</v>
       </c>
       <c r="D149">
-        <v>500</v>
+        <v>875</v>
       </c>
       <c r="E149">
         <v>2</v>
       </c>
       <c r="F149" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G149">
         <v>1</v>
@@ -4047,16 +4040,16 @@
         <v>4</v>
       </c>
       <c r="C150">
-        <v>10301</v>
+        <v>10201</v>
       </c>
       <c r="D150">
-        <v>500</v>
+        <v>875</v>
       </c>
       <c r="E150">
         <v>2</v>
       </c>
       <c r="F150" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -4070,16 +4063,16 @@
         <v>4</v>
       </c>
       <c r="C151">
-        <v>10301</v>
+        <v>10201</v>
       </c>
       <c r="D151">
-        <v>500</v>
+        <v>875</v>
       </c>
       <c r="E151">
         <v>2</v>
       </c>
       <c r="F151" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G151">
         <v>1</v>
@@ -4093,16 +4086,16 @@
         <v>4</v>
       </c>
       <c r="C152">
-        <v>10301</v>
+        <v>10201</v>
       </c>
       <c r="D152">
-        <v>6500</v>
+        <v>875</v>
       </c>
       <c r="E152">
         <v>2</v>
       </c>
       <c r="F152" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="G152">
         <v>1</v>
@@ -4116,16 +4109,16 @@
         <v>4</v>
       </c>
       <c r="C153">
-        <v>10302</v>
+        <v>10201</v>
       </c>
       <c r="D153">
-        <v>1</v>
+        <v>875</v>
       </c>
       <c r="E153">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F153" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="G153">
         <v>1</v>
@@ -4139,16 +4132,16 @@
         <v>4</v>
       </c>
       <c r="C154">
-        <v>10302</v>
+        <v>10201</v>
       </c>
       <c r="D154">
-        <v>1</v>
+        <v>875</v>
       </c>
       <c r="E154">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F154" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="G154">
         <v>1</v>
@@ -4162,13 +4155,13 @@
         <v>4</v>
       </c>
       <c r="C155">
-        <v>10302</v>
+        <v>10201</v>
       </c>
       <c r="D155">
-        <v>1</v>
+        <v>875</v>
       </c>
       <c r="E155">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F155" t="s">
         <v>45</v>
@@ -4185,13 +4178,13 @@
         <v>4</v>
       </c>
       <c r="C156">
-        <v>10302</v>
+        <v>10201</v>
       </c>
       <c r="D156">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="E156">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F156" t="s">
         <v>46</v>
@@ -4208,13 +4201,13 @@
         <v>4</v>
       </c>
       <c r="C157">
-        <v>10302</v>
+        <v>10201</v>
       </c>
       <c r="D157">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="E157">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F157" t="s">
         <v>47</v>
@@ -4231,13 +4224,13 @@
         <v>4</v>
       </c>
       <c r="C158">
-        <v>10302</v>
+        <v>10201</v>
       </c>
       <c r="D158">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="E158">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F158" t="s">
         <v>48</v>
@@ -4254,16 +4247,16 @@
         <v>4</v>
       </c>
       <c r="C159">
-        <v>10302</v>
+        <v>10301</v>
       </c>
       <c r="D159">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="E159">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F159" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="G159">
         <v>1</v>
@@ -4277,16 +4270,16 @@
         <v>4</v>
       </c>
       <c r="C160">
-        <v>10302</v>
+        <v>10301</v>
       </c>
       <c r="D160">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="E160">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F160" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G160">
         <v>1</v>
@@ -4300,16 +4293,16 @@
         <v>4</v>
       </c>
       <c r="C161">
-        <v>10302</v>
+        <v>10301</v>
       </c>
       <c r="D161">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="E161">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F161" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G161">
         <v>1</v>
@@ -4323,16 +4316,16 @@
         <v>4</v>
       </c>
       <c r="C162">
-        <v>10302</v>
+        <v>10301</v>
       </c>
       <c r="D162">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="E162">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F162" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="G162">
         <v>1</v>
@@ -4346,16 +4339,16 @@
         <v>4</v>
       </c>
       <c r="C163">
-        <v>10302</v>
+        <v>10301</v>
       </c>
       <c r="D163">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="E163">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F163" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="G163">
         <v>1</v>
@@ -4369,16 +4362,16 @@
         <v>4</v>
       </c>
       <c r="C164">
-        <v>10302</v>
+        <v>10301</v>
       </c>
       <c r="D164">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="E164">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F164" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G164">
         <v>1</v>
@@ -4392,16 +4385,16 @@
         <v>4</v>
       </c>
       <c r="C165">
-        <v>10302</v>
+        <v>10301</v>
       </c>
       <c r="D165">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="E165">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F165" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="G165">
         <v>1</v>
@@ -4415,16 +4408,16 @@
         <v>4</v>
       </c>
       <c r="C166">
-        <v>10302</v>
+        <v>10301</v>
       </c>
       <c r="D166">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="E166">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F166" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G166">
         <v>1</v>
@@ -4438,16 +4431,16 @@
         <v>4</v>
       </c>
       <c r="C167">
-        <v>10302</v>
+        <v>10301</v>
       </c>
       <c r="D167">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="E167">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F167" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G167">
         <v>1</v>
@@ -4461,16 +4454,16 @@
         <v>4</v>
       </c>
       <c r="C168">
-        <v>10302</v>
+        <v>10301</v>
       </c>
       <c r="D168">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="E168">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F168" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G168">
         <v>1</v>
@@ -4484,16 +4477,16 @@
         <v>4</v>
       </c>
       <c r="C169">
-        <v>10302</v>
+        <v>10301</v>
       </c>
       <c r="D169">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="E169">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F169" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G169">
         <v>1</v>
@@ -4516,7 +4509,7 @@
         <v>3</v>
       </c>
       <c r="F170" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="G170">
         <v>1</v>
@@ -4539,9 +4532,170 @@
         <v>3</v>
       </c>
       <c r="F171" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>4</v>
+      </c>
+      <c r="C172">
+        <v>10302</v>
+      </c>
+      <c r="D172">
+        <v>1</v>
+      </c>
+      <c r="E172">
+        <v>3</v>
+      </c>
+      <c r="F172" t="s">
+        <v>53</v>
+      </c>
+      <c r="G172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>4</v>
+      </c>
+      <c r="C173">
+        <v>10302</v>
+      </c>
+      <c r="D173">
+        <v>1</v>
+      </c>
+      <c r="E173">
+        <v>3</v>
+      </c>
+      <c r="F173" t="s">
+        <v>54</v>
+      </c>
+      <c r="G173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>4</v>
+      </c>
+      <c r="C174">
+        <v>10302</v>
+      </c>
+      <c r="D174">
+        <v>1</v>
+      </c>
+      <c r="E174">
+        <v>3</v>
+      </c>
+      <c r="F174" t="s">
+        <v>55</v>
+      </c>
+      <c r="G174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>4</v>
+      </c>
+      <c r="C175">
+        <v>10302</v>
+      </c>
+      <c r="D175">
+        <v>1</v>
+      </c>
+      <c r="E175">
+        <v>3</v>
+      </c>
+      <c r="F175" t="s">
+        <v>56</v>
+      </c>
+      <c r="G175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>4</v>
+      </c>
+      <c r="C176">
+        <v>10302</v>
+      </c>
+      <c r="D176">
+        <v>1</v>
+      </c>
+      <c r="E176">
+        <v>3</v>
+      </c>
+      <c r="F176" t="s">
+        <v>57</v>
+      </c>
+      <c r="G176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>4</v>
+      </c>
+      <c r="C177">
+        <v>10302</v>
+      </c>
+      <c r="D177">
+        <v>1</v>
+      </c>
+      <c r="E177">
+        <v>3</v>
+      </c>
+      <c r="F177" t="s">
+        <v>58</v>
+      </c>
+      <c r="G177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>4</v>
+      </c>
+      <c r="C178">
+        <v>10302</v>
+      </c>
+      <c r="D178">
+        <v>1</v>
+      </c>
+      <c r="E178">
+        <v>3</v>
+      </c>
+      <c r="F178" t="s">
+        <v>59</v>
+      </c>
+      <c r="G178">
         <v>1</v>
       </c>
     </row>
